--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Best Trades" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Annual Perf" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Equity Curve" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sat By Ticker" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4061,17 +4062,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bear Sat</t>
+          <t>Bear Mode</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Defensive universe</t>
+          <t>Cash total</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Defensive universe</t>
+          <t>Cash total</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -4100,7 +4101,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>159.5%</t>
+          <t>159.3%</t>
         </is>
       </c>
     </row>
@@ -40415,4 +40416,1294 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>WR%</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total PnL%</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg PnL%</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Stop Loss</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Take Profit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>HIMS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>176.4%</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>17.6%</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>RIOT</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>159.4%</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>53.1%</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>139.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>BNTX</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>127.9%</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>FAS</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>114.2%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8.2%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>HUT</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86.7%</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8.7%</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84.0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9.3%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SOUN</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>70.1%</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14.0%</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>LABU</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>60.2%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30.1%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>UPRO</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>DKNG</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>44.5%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4.9%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>MARA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43.1%</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10.8%</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SPXL</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37.4%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31.1%</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23.3%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>18.4%</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ARKK</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>18.4%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4.6%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TQQQ</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>16.3%</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>10.8%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>10.2%</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>8.6%</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1.1%</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>TECL</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>CLSK</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>-4.9%</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>-1.0%</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>-10.0%</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>ASTS</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>-13.0%</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>-1.6%</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>-14.8%</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>-3.7%</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>IONQ</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>-21.5%</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>-25.9%</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>-5.2%</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>-26.2%</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>-5.2%</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TNA</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>-30.2%</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>-10.1%</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>MRNA</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>-35.6%</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>RIVN</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>-49.9%</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>-16.6%</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>